--- a/data/ImJai_Database.xlsx
+++ b/data/ImJai_Database.xlsx
@@ -1125,7 +1125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1179,6 +1179,11 @@
           <t>promotion</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>is_recommended</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1216,7 +1221,11 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1259,6 +1268,11 @@
           <t>ซื้อกาแฟ/ชา 1 แก้ว + เบเกอรี 1 ชิ้น (DS-01/DS-02) ลด 15 บาท ถึง 31 ส.ค. 2569</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1301,6 +1315,11 @@
           <t>ซื้อกาแฟ/ชา 1 แก้ว + เบเกอรี 1 ชิ้น (DS-01/DS-02) ลด 15 บาท ถึง 31 ส.ค. 2569</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1343,6 +1362,11 @@
           <t>ซื้อกาแฟ/ชา 1 แก้ว + เบเกอรี 1 ชิ้น (DS-01/DS-02) ลด 15 บาท ถึง 31 ส.ค. 2569</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1380,7 +1404,11 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1423,6 +1451,11 @@
           <t>ซื้อกาแฟ/ชา 1 แก้ว + เบเกอรี 1 ชิ้น (DS-01/DS-02) ลด 15 บาท ถึง 31 ส.ค. 2569</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1465,6 +1498,11 @@
           <t>ซื้อกาแฟ/ชา 1 แก้ว + เบเกอรี 1 ชิ้น (DS-01/DS-02) ลด 15 บาท ถึง 31 ส.ค. 2569</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1502,7 +1540,11 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1540,7 +1582,11 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1578,7 +1624,11 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1616,7 +1666,11 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1654,7 +1708,11 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1692,7 +1750,11 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1730,7 +1792,11 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1773,6 +1839,11 @@
           <t>ซื้อกาแฟ/ชา 1 แก้ว + เบเกอรี 1 ชิ้น (DS-01/DS-02) ลด 15 บาท ถึง 31 ส.ค. 2569</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1815,6 +1886,11 @@
           <t>ซื้อกาแฟ/ชา 1 แก้ว + เบเกอรี 1 ชิ้น (DS-01/DS-02) ลด 15 บาท ถึง 31 ส.ค. 2569</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1852,7 +1928,11 @@
           <t>TRUE</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1865,7 +1945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1937,6 +2017,21 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>payment_status</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>payment_ref</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>paid_at</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1992,6 +2087,153 @@
       <c r="K2" t="inlineStr">
         <is>
           <t>แถวตัวอย่าง ลบทิ้งได้</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>รอชำระเงิน</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ORD-20260820-171500</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-08-20 17:15:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Udef456line</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>คุณเบล</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>082-345-6789</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ข้าวผัดกะเพราหมูสับ ไข่ดาว x1, อเมริกาโน่เย็น x1</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>135</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>delivery</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>กำลังจัดส่ง</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>แถวตัวอย่าง ลบทิ้งได้</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>ชำระแล้ว</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>TXN-DEMO-001</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2026-08-20 17:16:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ORD-20260819-201000</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-08-19 20:10:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ughi789line</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>คุณต้น</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>083-456-7890</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>สปาเกตตีคาโบนารา x1, ชาไทยเย็น x1</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>200</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>pickup</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ลูกค้ารับแล้ว</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>20:35</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>แถวตัวอย่าง ลบทิ้งได้</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>ชำระแล้ว</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>TXN-DEMO-002</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2026-08-19 20:11:05</t>
         </is>
       </c>
     </row>
